--- a/CapNhatTienDo.xlsx
+++ b/CapNhatTienDo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Cty ĐL VungTau\1. TCKT_PCVT\4. Công nghệ AI\KT SCL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A1BDA0-8520-4018-898E-EB8F6804FD8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285C68CE-F24B-4A5E-9FDE-2C940010C534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{900D08F0-E626-4B53-85E3-E59042101309}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{900D08F0-E626-4B53-85E3-E59042101309}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="52">
   <si>
     <t>STT</t>
   </si>
@@ -119,9 +119,6 @@
 - QT: 9/2026</t>
   </si>
   <si>
-    <t>mới giao xe</t>
-  </si>
-  <si>
     <t>VTAD2610001</t>
   </si>
   <si>
@@ -147,11 +144,6 @@
 - QT: 7/2026</t>
   </si>
   <si>
-    <t>TI hạ thế: 42%
-TI Trung thế: 24%
-TU: 26%</t>
-  </si>
-  <si>
     <t>đã xử lý được 43 vị trí xự cố</t>
   </si>
   <si>
@@ -197,12 +189,6 @@
     <t>Đang chờ Thẩm định KH LCNT</t>
   </si>
   <si>
-    <t>Thứ 2 (18/5) ký HĐ</t>
-  </si>
-  <si>
-    <t>dự kiến 20/5 thi công</t>
-  </si>
-  <si>
     <t>Đã thực hiện</t>
   </si>
   <si>
@@ -210,6 +196,14 @@
   </si>
   <si>
     <t>Giá trị HĐ</t>
+  </si>
+  <si>
+    <t>Đã khởi công</t>
+  </si>
+  <si>
+    <t>TI hạ thế: 48,8%, thay được 496/961
+TI Trung thế: 24,7%, thay được: 152/615
+TU: 33%, thay được 203/615</t>
   </si>
 </sst>
 </file>
@@ -217,8 +211,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -288,9 +282,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -307,7 +301,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -325,16 +319,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -356,9 +347,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -396,7 +387,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -502,7 +493,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -644,7 +635,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -653,22 +644,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8E70228-6DFF-4518-BC54-CE130EECE97A}">
   <dimension ref="A2:P19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.6328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.453125" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.26953125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="39.36328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.1796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.08984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31" style="10" customWidth="1"/>
-    <col min="8" max="8" width="19.1796875" style="10" customWidth="1"/>
-    <col min="9" max="17" width="12.08984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="13.1796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="8.7265625" style="10"/>
+    <col min="1" max="1" width="4.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.21875" style="10" customWidth="1"/>
+    <col min="4" max="4" width="39.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" style="10" customWidth="1"/>
+    <col min="6" max="6" width="21.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.88671875" style="10" customWidth="1"/>
+    <col min="8" max="8" width="19.21875" style="10" customWidth="1"/>
+    <col min="9" max="17" width="12.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="13.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="8.77734375" style="10"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" s="3" customFormat="1" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" s="3" customFormat="1" ht="35.549999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -688,13 +679,13 @@
         <v>5</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -720,7 +711,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="3" customFormat="1" ht="42" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" s="3" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -740,13 +731,13 @@
         <v>10</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:16" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -766,11 +757,11 @@
         <v>10</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" spans="1:16" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -790,11 +781,11 @@
         <v>21</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H6" s="5"/>
     </row>
-    <row r="7" spans="1:16" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -813,51 +804,49 @@
       <c r="F7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>25</v>
+      <c r="G7" s="7">
+        <v>0.5</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:16" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="E8" s="6">
         <v>13236612376</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H8" s="8" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+      <c r="H8" s="8"/>
+    </row>
+    <row r="9" spans="1:16" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>32</v>
       </c>
       <c r="E9" s="6">
         <v>5780025934</v>
@@ -866,71 +855,67 @@
         <v>10</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H9" s="5"/>
     </row>
-    <row r="10" spans="1:16" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="E10" s="14"/>
       <c r="G10" s="12"/>
-      <c r="H10" s="13"/>
-    </row>
-    <row r="12" spans="1:16" s="3" customFormat="1" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:16" s="3" customFormat="1" ht="35.549999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="H12" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="I12" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="J12" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="K12" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="L12" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="M12" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="L12" s="11" t="s">
+      <c r="N12" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="M12" s="11" t="s">
+      <c r="O12" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="N12" s="11" t="s">
+      <c r="P12" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="O12" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="P12" s="11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:16" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>1</v>
       </c>
@@ -956,7 +941,7 @@
       <c r="O13" s="5"/>
       <c r="P13" s="5"/>
     </row>
-    <row r="14" spans="1:16" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>2</v>
       </c>
@@ -967,7 +952,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="5">
-        <v>0</v>
+        <v>11.706</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="5"/>
@@ -982,7 +967,7 @@
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
     </row>
-    <row r="15" spans="1:16" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>3</v>
       </c>
@@ -1008,7 +993,7 @@
       <c r="O15" s="5"/>
       <c r="P15" s="5"/>
     </row>
-    <row r="16" spans="1:16" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>4</v>
       </c>
@@ -1034,7 +1019,7 @@
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
     </row>
-    <row r="17" spans="1:16" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>5</v>
       </c>
@@ -1045,7 +1030,7 @@
         <v>23</v>
       </c>
       <c r="D17" s="5">
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="5"/>
@@ -1060,18 +1045,18 @@
       <c r="O17" s="5"/>
       <c r="P17" s="5"/>
     </row>
-    <row r="18" spans="1:16" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>6</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="D18" s="5">
-        <v>0</v>
+        <v>12.839</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="5"/>
@@ -1086,18 +1071,18 @@
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
     </row>
-    <row r="19" spans="1:16" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>7</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="D19" s="5">
-        <v>4.827</v>
+        <v>4.8280000000000003</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="5"/>
